--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484156_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484156_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0142</v>
+        <v>4.5065</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9345</v>
+        <v>3.3426</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0797</v>
+        <v>1.1639</v>
       </c>
       <c r="G2" t="n">
         <v>3.6633</v>
@@ -610,13 +610,13 @@
         <v>1.3887</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.165</v>
+        <v>0.3273</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2153</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4585</v>
+        <v>0.5426</v>
       </c>
       <c r="V2" t="n">
         <v>-0.6745</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9139</v>
+        <v>4.2784</v>
       </c>
       <c r="E3" t="n">
-        <v>5.196</v>
+        <v>5.7288</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2821</v>
+        <v>-1.4504</v>
       </c>
       <c r="G3" t="n">
         <v>2.0938</v>
@@ -688,13 +688,13 @@
         <v>1.3887</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0635</v>
+        <v>0.4279</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.68</v>
+        <v>-0.1472</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7435</v>
+        <v>0.5752</v>
       </c>
       <c r="V3" t="n">
         <v>1.955</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9693</v>
+        <v>1.1426</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2047</v>
+        <v>0.5594</v>
       </c>
       <c r="G4" t="n">
         <v>0.3485</v>
@@ -766,13 +766,13 @@
         <v>0.7935</v>
       </c>
       <c r="S4" t="n">
-        <v>1.684</v>
+        <v>0.8573</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1135</v>
+        <v>-0.0679</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5705</v>
+        <v>0.9252</v>
       </c>
       <c r="V4" t="n">
         <v>0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3588</v>
+        <v>-0.178</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1753</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5341</v>
+        <v>-0.478</v>
       </c>
       <c r="G5" t="n">
         <v>-1.5667</v>
@@ -844,13 +844,13 @@
         <v>0.7935</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0249</v>
+        <v>0.1559</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2436</v>
+        <v>-0.1189</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2187</v>
+        <v>0.2748</v>
       </c>
       <c r="V5" t="n">
         <v>2.0263</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1743</v>
+        <v>-0.83</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9335</v>
+        <v>-0.7294</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2408</v>
+        <v>-0.1006</v>
       </c>
       <c r="G6" t="n">
         <v>-1.2168</v>
@@ -922,13 +922,13 @@
         <v>0.3968</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3542</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3741</v>
+        <v>-0.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0198</v>
+        <v>0.1601</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMES CORREIA</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4125</v>
+        <v>-2.1928</v>
       </c>
       <c r="E7" t="n">
-        <v>1.329</v>
+        <v>-1.3696</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7416</v>
+        <v>-0.8232</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.2632</v>
+        <v>-1.921</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8767</v>
+        <v>-0.5645</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3865</v>
+        <v>-1.3564</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5072</v>
+        <v>-1.1996</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0421</v>
+        <v>-0.6399</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5349</v>
+        <v>-0.5597</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.756</v>
+        <v>-0.7214</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1653</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.9213</v>
+        <v>-0.7967</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5952</v>
+        <v>-0.1984</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1903</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3167</v>
+        <v>0.1148</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1654</v>
+        <v>0.0284</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1512</v>
+        <v>0.0864</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0611</v>
+        <v>-0.3866</v>
       </c>
       <c r="W7" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3271</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>A. GOMES CORREIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5496</v>
+        <v>-2.4637</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6983</v>
+        <v>0.0253</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8512999999999999</v>
+        <v>-2.4891</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.921</v>
+        <v>-3.2632</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5645</v>
+        <v>-0.8767</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3564</v>
+        <v>-2.3865</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1996</v>
+        <v>-0.5072</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6399</v>
+        <v>-1.0421</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5597</v>
+        <v>0.5349</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7214</v>
+        <v>-2.756</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.1653</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7967</v>
+        <v>-2.9213</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1984</v>
+        <v>-0.5952</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>1.1903</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.242</v>
+        <v>1.2654</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3004</v>
+        <v>0.8617</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0584</v>
+        <v>0.4037</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3866</v>
+        <v>-1.0611</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3866</v>
+        <v>-1.3271</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.275</v>
+        <v>-2.5047</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.749</v>
+        <v>-1.0347</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5261</v>
+        <v>-1.47</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1731</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3084</v>
+        <v>0.462</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4364</v>
+        <v>0.2778</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1281</v>
+        <v>0.1842</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4897</v>
+        <v>-3.3035</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7313</v>
+        <v>-0.6292</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7584</v>
+        <v>-2.6742</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6899</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6014</v>
+        <v>-0.4152</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3117</v>
+        <v>-0.2097</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2897</v>
+        <v>-0.2055</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2065</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.1159</v>
+        <v>-5.3098</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6869</v>
+        <v>-1.993</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.4291</v>
+        <v>-3.3168</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9795</v>
@@ -1312,13 +1312,13 @@
         <v>1.3887</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9761</v>
+        <v>0.7822</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7483</v>
+        <v>0.4422</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2278</v>
+        <v>0.34</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3271</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.478400000000001</v>
+        <v>-6.854999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>3.600399999999999</v>
+        <v>4.224000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.0791</v>
+        <v>-11.079</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.704600000000001</v>
+        <v>-7.704599999999999</v>
       </c>
       <c r="H12" t="n">
         <v>3.0487</v>
@@ -1390,13 +1390,13 @@
         <v>7.9354</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3444</v>
+        <v>3.9677</v>
       </c>
       <c r="T12" t="n">
-        <v>0.05749999999999977</v>
+        <v>0.6811</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2868</v>
+        <v>3.2867</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1425000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3386</v>
+        <v>4.9746</v>
       </c>
       <c r="E13" t="n">
-        <v>4.125</v>
+        <v>4.7372</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2136</v>
+        <v>0.2374</v>
       </c>
       <c r="G13" t="n">
         <v>4.0045</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6417</v>
+        <v>-0.0057</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2979</v>
+        <v>-0.6857</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6562</v>
+        <v>0.68</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. PUIG DE GRACIA</t>
+          <t>R. VERANO FORES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8713</v>
+        <v>3.8105</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8411</v>
+        <v>4.2177</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0302</v>
+        <v>-0.4072</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3061</v>
+        <v>2.6915</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1759</v>
+        <v>0.5694</v>
       </c>
       <c r="I14" t="n">
-        <v>4.1301</v>
+        <v>2.1221</v>
       </c>
       <c r="J14" t="n">
-        <v>5.3505</v>
+        <v>4.0226</v>
       </c>
       <c r="K14" t="n">
         <v>0.9678</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3827</v>
+        <v>3.0548</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0444</v>
+        <v>-1.3311</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.3983</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2526</v>
+        <v>-0.9328</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.579</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.1741</v>
+        <v>-0.1984</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2687</v>
+        <v>-0.1587</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7481</v>
+        <v>-0.2097</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4794</v>
+        <v>0.051</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4129</v>
+        <v>1.2777</v>
       </c>
       <c r="W14" t="n">
-        <v>2.4129</v>
+        <v>0.6032</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. VERANO FORES</t>
+          <t>M. PUIG DE GRACIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4602</v>
+        <v>3.7489</v>
       </c>
       <c r="E15" t="n">
-        <v>4.1157</v>
+        <v>3.9431</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6555</v>
+        <v>-0.1942</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6915</v>
+        <v>4.3061</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5694</v>
+        <v>0.1759</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1221</v>
+        <v>4.1301</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0226</v>
+        <v>5.3505</v>
       </c>
       <c r="K15" t="n">
         <v>0.9678</v>
       </c>
       <c r="L15" t="n">
-        <v>3.0548</v>
+        <v>4.3827</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3311</v>
+        <v>-1.0444</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3983</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9328</v>
+        <v>-0.2526</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-2.579</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1984</v>
+        <v>-3.1741</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1984</v>
+        <v>0.5952</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.509</v>
+        <v>-0.3911</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3117</v>
+        <v>-0.6461</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1973</v>
+        <v>0.255</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2777</v>
+        <v>2.4129</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6032</v>
+        <v>2.4129</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.717</v>
+        <v>2.0894</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2751</v>
+        <v>3.4792</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5581</v>
+        <v>-1.3898</v>
       </c>
       <c r="G16" t="n">
         <v>3.5149</v>
@@ -1702,13 +1702,13 @@
         <v>0.3968</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2028</v>
+        <v>-0.8304</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4988</v>
+        <v>-0.2947</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.704</v>
+        <v>-0.5357</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.975</v>
+        <v>0.7386</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4971</v>
+        <v>-0.7012</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4721</v>
+        <v>1.4398</v>
       </c>
       <c r="G17" t="n">
         <v>-0.88</v>
@@ -1780,13 +1780,13 @@
         <v>1.5871</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7323</v>
+        <v>0.496</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0057</v>
+        <v>-0.1983</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7266</v>
+        <v>0.6943</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SANTIAGO PAZ</t>
+          <t>A. CORTEGANO NAVARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3404</v>
+        <v>0.2687</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3791</v>
+        <v>-0.4691</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0387</v>
+        <v>0.7378</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9639</v>
+        <v>-1.6916</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2244</v>
+        <v>0.187</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1882</v>
+        <v>-1.8785</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9888</v>
+        <v>-1.3371</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7046</v>
+        <v>-0.0998</v>
       </c>
       <c r="L18" t="n">
-        <v>2.6934</v>
+        <v>-1.2374</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0249</v>
+        <v>-0.3545</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5197000000000001</v>
+        <v>0.2867</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5051</v>
+        <v>-0.6412</v>
       </c>
       <c r="P18" t="n">
+        <v>1.5871</v>
+      </c>
+      <c r="Q18" t="n">
         <v>-0.1984</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-1.9838</v>
       </c>
       <c r="R18" t="n">
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4251</v>
+        <v>-0.1587</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3742</v>
+        <v>-0.6007</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7993</v>
+        <v>0.442</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.6671</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.1352</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. DIAZ SANCHEZ</t>
+          <t>P. SANTIAGO PAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3341</v>
+        <v>0.2129</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.029</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5384</v>
+        <v>0.2418</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8683</v>
+        <v>0.9639</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5995</v>
+        <v>-1.2244</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4679</v>
+        <v>2.1882</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1811</v>
+        <v>1.9888</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3735</v>
+        <v>-0.7046</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5546</v>
+        <v>2.6934</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6872</v>
+        <v>-1.0249</v>
       </c>
       <c r="N19" t="n">
-        <v>0.226</v>
+        <v>-0.5197000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9133</v>
+        <v>-0.5051</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5871</v>
+        <v>-0.1984</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1984</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
         <v>1.7855</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1837</v>
+        <v>-0.5526</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.493</v>
+        <v>-0.0339</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3093</v>
+        <v>-0.5187</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CORTEGANO NAVARRO</t>
+          <t>R. DIAZ SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6019</v>
+        <v>-0.3205</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9792</v>
+        <v>-0.7705</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3773</v>
+        <v>0.45</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6916</v>
+        <v>-0.8683</v>
       </c>
       <c r="H20" t="n">
-        <v>0.187</v>
+        <v>0.5995</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8785</v>
+        <v>-1.4679</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3371</v>
+        <v>-0.1811</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0998</v>
+        <v>0.3735</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2374</v>
+        <v>-0.5546</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3545</v>
+        <v>-0.6872</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2867</v>
+        <v>0.226</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6412</v>
+        <v>-0.9133</v>
       </c>
       <c r="P20" t="n">
         <v>1.5871</v>
@@ -2014,22 +2014,22 @@
         <v>1.7855</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0293</v>
+        <v>-0.17</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1109</v>
+        <v>-0.391</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0815</v>
+        <v>0.2209</v>
       </c>
       <c r="V20" t="n">
-        <v>0.532</v>
+        <v>-0.8692</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6671</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1352</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1957</v>
+        <v>-2.9482</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8351</v>
+        <v>-1.4473</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3606</v>
+        <v>-1.5009</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4965</v>
@@ -2092,13 +2092,13 @@
         <v>0.5952</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2296</v>
+        <v>-0.5229</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4876</v>
+        <v>-0.1246</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.258</v>
+        <v>-0.3983</v>
       </c>
       <c r="V21" t="n">
         <v>-0.532</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0923</v>
+        <v>-4.4162</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4732</v>
+        <v>-1.8813</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6191</v>
+        <v>-2.535</v>
       </c>
       <c r="G22" t="n">
         <v>-2.8399</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0459</v>
+        <v>-0.3698</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3061</v>
+        <v>-0.102</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.352</v>
+        <v>-0.2678</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2065</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>7.4785</v>
+        <v>8.1587</v>
       </c>
       <c r="E23" t="n">
-        <v>11.0789</v>
+        <v>11.0788</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6004</v>
+        <v>-2.9203</v>
       </c>
       <c r="G23" t="n">
         <v>7.704600000000001</v>
@@ -2230,7 +2230,7 @@
         <v>16.5823</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.706999999999999</v>
+        <v>-8.707000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-2.8776</v>
@@ -2242,19 +2242,19 @@
         <v>2.9757</v>
       </c>
       <c r="Q23" t="n">
-        <v>-7.9353</v>
+        <v>-7.935300000000001</v>
       </c>
       <c r="R23" t="n">
         <v>10.9114</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.3443</v>
+        <v>-2.6639</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.286800000000001</v>
+        <v>-3.2867</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.05759999999999998</v>
+        <v>0.6227000000000003</v>
       </c>
       <c r="V23" t="n">
         <v>0.1424000000000003</v>
